--- a/data/trans_orig/KIDM_C_3_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_3_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>17452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100098</t>
+          <t>99696</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108060</t>
+          <t>107964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114057</t>
+          <t>113629</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121134</t>
+          <t>121044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>216970</t>
+          <t>217740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227792</t>
+          <t>227954</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>24259</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>163537</t>
+          <t>164084</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173601</t>
+          <t>173709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>172496</t>
+          <t>172740</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182094</t>
+          <t>181652</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>340381</t>
+          <t>340119</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>353581</t>
+          <t>353126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>22453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>20944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37446</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>267627</t>
+          <t>267539</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279758</t>
+          <t>280023</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>290262</t>
+          <t>290893</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>301527</t>
+          <t>301950</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>562125</t>
+          <t>562427</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>579142</t>
+          <t>578627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2012 (tasa de respuesta: 95,41%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2012 (tasa de respuesta: 95,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>19946</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34779</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>26059</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>36106</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57295</t>
+          <t>57311</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115186</t>
+          <t>114285</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130833</t>
+          <t>130019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126595</t>
+          <t>127804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140781</t>
+          <t>140738</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>246533</t>
+          <t>246517</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>267574</t>
+          <t>267722</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14014</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>28732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12814</t>
+          <t>13033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25734</t>
+          <t>26626</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31228</t>
+          <t>30938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>49530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133982</t>
+          <t>133477</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148195</t>
+          <t>147428</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144272</t>
+          <t>143380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>157192</t>
+          <t>156973</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>281973</t>
+          <t>282685</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>300987</t>
+          <t>301277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>38490</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58394</t>
+          <t>59050</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28717</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48243</t>
+          <t>48894</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72079</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100496</t>
+          <t>100119</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>253780</t>
+          <t>253124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>274935</t>
+          <t>273684</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275626</t>
+          <t>274975</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>295152</t>
+          <t>295013</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>535547</t>
+          <t>535924</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>563964</t>
+          <t>563372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>22574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10945</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>23890</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23628</t>
+          <t>23193</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40278</t>
+          <t>40958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>158803</t>
+          <t>158313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>171089</t>
+          <t>170780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154621</t>
+          <t>154721</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167666</t>
+          <t>167611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>319220</t>
+          <t>318540</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>335870</t>
+          <t>336305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23333</t>
+          <t>23920</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26603</t>
+          <t>25909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26594</t>
+          <t>27088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46303</t>
+          <t>46343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>141474</t>
+          <t>140887</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153993</t>
+          <t>154518</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>143989</t>
+          <t>144683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>157713</t>
+          <t>157569</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>289096</t>
+          <t>289056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>308805</t>
+          <t>308311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -3937,12 +3937,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22477</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40964</t>
+          <t>41274</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26171</t>
+          <t>26540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44589</t>
+          <t>45214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54592</t>
+          <t>54564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79978</t>
+          <t>79629</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304730</t>
+          <t>304420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>323217</t>
+          <t>322406</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>304614</t>
+          <t>303989</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323032</t>
+          <t>322663</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>614919</t>
+          <t>615268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640305</t>
+          <t>640333</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2023 (tasa de respuesta: 99,65%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61257</t>
+          <t>61302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67098</t>
+          <t>67180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90270</t>
+          <t>90349</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98007</t>
+          <t>98040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154808</t>
+          <t>154975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164140</t>
+          <t>164204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>12194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4966,12 +4966,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>131406</t>
+          <t>131591</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>140610</t>
+          <t>140785</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>167635</t>
+          <t>167095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>302054</t>
+          <t>301956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>311337</t>
+          <t>311083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>196989</t>
+          <t>196202</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>206875</t>
+          <t>206603</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>260482</t>
+          <t>260348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>268824</t>
+          <t>268826</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>459965</t>
+          <t>460629</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>472950</t>
+          <t>474059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5394,12 +5394,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
